--- a/tasks/AnalyticalCase/output/WeeklyEffortPerProject.xlsx
+++ b/tasks/AnalyticalCase/output/WeeklyEffortPerProject.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="361">
   <si>
     <t>Project_Week</t>
   </si>
@@ -29,12 +29,6 @@
     <t>PRJ117_W14_2025</t>
   </si>
   <si>
-    <t>PRJ160_W22_2025</t>
-  </si>
-  <si>
-    <t>PRJ136_W13_2025</t>
-  </si>
-  <si>
     <t>PRJ110_W16_2025</t>
   </si>
   <si>
@@ -50,6 +44,9 @@
     <t>PRJ192_W11_2025</t>
   </si>
   <si>
+    <t>PRJ107_W16_2025</t>
+  </si>
+  <si>
     <t>PRJ188_W12_2025</t>
   </si>
   <si>
@@ -83,18 +80,12 @@
     <t>PRJ159_W15_2025</t>
   </si>
   <si>
-    <t>PRJ157_W19_2025</t>
-  </si>
-  <si>
     <t>PRJ143_W16_2025</t>
   </si>
   <si>
     <t>PRJ185_W22_2025</t>
   </si>
   <si>
-    <t>PRJ195_W15_2025</t>
-  </si>
-  <si>
     <t>PRJ129_W19_2025</t>
   </si>
   <si>
@@ -122,15 +113,15 @@
     <t>PRJ110_W14_2025</t>
   </si>
   <si>
+    <t>PRJ180_W20_2025</t>
+  </si>
+  <si>
     <t>PRJ124_W19_2025</t>
   </si>
   <si>
     <t>PRJ147_W10_2025</t>
   </si>
   <si>
-    <t>PRJ126_W15_2025</t>
-  </si>
-  <si>
     <t>PRJ139_W22_2025</t>
   </si>
   <si>
@@ -143,9 +134,6 @@
     <t>PRJ161_W18_2025</t>
   </si>
   <si>
-    <t>PRJ159_W13_2025</t>
-  </si>
-  <si>
     <t>PRJ169_W11_2025</t>
   </si>
   <si>
@@ -161,6 +149,9 @@
     <t>PRJ106_W19_2025</t>
   </si>
   <si>
+    <t>PRJ143_W14_2025</t>
+  </si>
+  <si>
     <t>PRJ193_W20_2025</t>
   </si>
   <si>
@@ -176,9 +167,6 @@
     <t>PRJ111_W17_2025</t>
   </si>
   <si>
-    <t>PRJ183_W19_2025</t>
-  </si>
-  <si>
     <t>PRJ105_W11_2025</t>
   </si>
   <si>
@@ -194,9 +182,6 @@
     <t>PRJ196_W12_2025</t>
   </si>
   <si>
-    <t>PRJ191_W16_2025</t>
-  </si>
-  <si>
     <t>PRJ157_W10_2025</t>
   </si>
   <si>
@@ -212,15 +197,15 @@
     <t>PRJ106_W15_2025</t>
   </si>
   <si>
+    <t>PRJ111_W20_2025</t>
+  </si>
+  <si>
+    <t>PRJ153_W18_2025</t>
+  </si>
+  <si>
     <t>PRJ131_W13_2025</t>
   </si>
   <si>
-    <t>PRJ111_W20_2025</t>
-  </si>
-  <si>
-    <t>PRJ153_W18_2025</t>
-  </si>
-  <si>
     <t>PRJ128_W21_2025</t>
   </si>
   <si>
@@ -233,9 +218,6 @@
     <t>PRJ199_W21_2025</t>
   </si>
   <si>
-    <t>PRJ181_W12_2025</t>
-  </si>
-  <si>
     <t>PRJ180_W22_2025</t>
   </si>
   <si>
@@ -257,16 +239,13 @@
     <t>PRJ130_W14_2025</t>
   </si>
   <si>
-    <t>PRJ152_W13_2025</t>
-  </si>
-  <si>
     <t>PRJ188_W22_2025</t>
   </si>
   <si>
-    <t>PRJ183_W12_2025</t>
-  </si>
-  <si>
-    <t>PRJ155_W19_2025</t>
+    <t>PRJ107_W14_2025</t>
+  </si>
+  <si>
+    <t>PRJ138_W13_2025</t>
   </si>
   <si>
     <t>PRJ173_W14_2025</t>
@@ -275,6 +254,9 @@
     <t>PRJ165_W20_2025</t>
   </si>
   <si>
+    <t>PRJ118_W17_2025</t>
+  </si>
+  <si>
     <t>PRJ175_W15_2025</t>
   </si>
   <si>
@@ -299,12 +281,6 @@
     <t>PRJ191_W19_2025</t>
   </si>
   <si>
-    <t>PRJ148_W11_2025</t>
-  </si>
-  <si>
-    <t>PRJ160_W17_2025</t>
-  </si>
-  <si>
     <t>PRJ153_W12_2025</t>
   </si>
   <si>
@@ -320,24 +296,18 @@
     <t>PRJ117_W18_2025</t>
   </si>
   <si>
+    <t>PRJ110_W21_2025</t>
+  </si>
+  <si>
     <t>PRJ195_W17_2025</t>
   </si>
   <si>
-    <t>PRJ175_W14_2025</t>
-  </si>
-  <si>
-    <t>PRJ113_W16_2025</t>
-  </si>
-  <si>
     <t>PRJ118_W18_2025</t>
   </si>
   <si>
     <t>PRJ108_W22_2025</t>
   </si>
   <si>
-    <t>PRJ136_W21_2025</t>
-  </si>
-  <si>
     <t>PRJ160_W14_2025</t>
   </si>
   <si>
@@ -353,7 +323,7 @@
     <t>PRJ124_W12_2025</t>
   </si>
   <si>
-    <t>PRJ138_W14_2025</t>
+    <t>PRJ152_W12_2025</t>
   </si>
   <si>
     <t>PRJ105_W13_2025</t>
@@ -362,24 +332,36 @@
     <t>PRJ166_W13_2025</t>
   </si>
   <si>
-    <t>PRJ130_W18_2025</t>
-  </si>
-  <si>
     <t>PRJ178_W19_2025</t>
   </si>
   <si>
     <t>PRJ141_W14_2025</t>
   </si>
   <si>
+    <t>PRJ175_W13_2025</t>
+  </si>
+  <si>
     <t>PRJ192_W20_2025</t>
   </si>
   <si>
+    <t>PRJ197_W18_2025</t>
+  </si>
+  <si>
+    <t>PRJ129_W14_2025</t>
+  </si>
+  <si>
+    <t>PRJ136_W20_2025</t>
+  </si>
+  <si>
     <t>PRJ113_W15_2025</t>
   </si>
   <si>
     <t>PRJ147_W14_2025</t>
   </si>
   <si>
+    <t>PRJ171_W11_2025</t>
+  </si>
+  <si>
     <t>PRJ136_W18_2025</t>
   </si>
   <si>
@@ -395,9 +377,6 @@
     <t>PRJ102_W18_2025</t>
   </si>
   <si>
-    <t>PRJ174_W20_2025</t>
-  </si>
-  <si>
     <t>PRJ137_W18_2025</t>
   </si>
   <si>
@@ -419,18 +398,24 @@
     <t>PRJ102_W23_2025</t>
   </si>
   <si>
-    <t>PRJ119_W15_2025</t>
+    <t>PRJ155_W18_2025</t>
   </si>
   <si>
     <t>PRJ143_W23_2025</t>
   </si>
   <si>
+    <t>PRJ162_W12_2025</t>
+  </si>
+  <si>
     <t>PRJ183_W21_2025</t>
   </si>
   <si>
     <t>PRJ153_W19_2025</t>
   </si>
   <si>
+    <t>PRJ160_W16_2025</t>
+  </si>
+  <si>
     <t>PRJ149_W12_2025</t>
   </si>
   <si>
@@ -458,6 +443,9 @@
     <t>PRJ171_W19_2025</t>
   </si>
   <si>
+    <t>PRJ140_W22_2025</t>
+  </si>
+  <si>
     <t>PRJ126_W20_2025</t>
   </si>
   <si>
@@ -467,21 +455,21 @@
     <t>PRJ101_W21_2025</t>
   </si>
   <si>
-    <t>PRJ148_W16_2025</t>
-  </si>
-  <si>
     <t>PRJ114_W17_2025</t>
   </si>
   <si>
-    <t>PRJ137_W22_2025</t>
-  </si>
-  <si>
     <t>PRJ179_W15_2025</t>
   </si>
   <si>
+    <t>PRJ145_W10_2025</t>
+  </si>
+  <si>
     <t>PRJ168_W21_2025</t>
   </si>
   <si>
+    <t>PRJ148_W10_2025</t>
+  </si>
+  <si>
     <t>PRJ114_W11_2025</t>
   </si>
   <si>
@@ -491,10 +479,19 @@
     <t>PRJ162_W13_2025</t>
   </si>
   <si>
-    <t>PRJ137_W13_2025</t>
-  </si>
-  <si>
-    <t>PRJ140_W23_2025</t>
+    <t>PRJ159_W12_2025</t>
+  </si>
+  <si>
+    <t>PRJ190_W18_2025</t>
+  </si>
+  <si>
+    <t>PRJ123_W11_2025</t>
+  </si>
+  <si>
+    <t>PRJ165_W12_2025</t>
+  </si>
+  <si>
+    <t>PRJ168_W12_2025</t>
   </si>
   <si>
     <t>PRJ196_W17_2025</t>
@@ -503,18 +500,18 @@
     <t>PRJ165_W18_2025</t>
   </si>
   <si>
+    <t>PRJ171_W18_2025</t>
+  </si>
+  <si>
+    <t>PRJ148_W15_2025</t>
+  </si>
+  <si>
     <t>PRJ128_W13_2025</t>
   </si>
   <si>
-    <t>PRJ154_W15_2025</t>
-  </si>
-  <si>
     <t>PRJ105_W18_2025</t>
   </si>
   <si>
-    <t>PRJ124_W22_2025</t>
-  </si>
-  <si>
     <t>PRJ198_W15_2025</t>
   </si>
   <si>
@@ -539,9 +536,6 @@
     <t>PRJ142_W17_2025</t>
   </si>
   <si>
-    <t>PRJ171_W12_2025</t>
-  </si>
-  <si>
     <t>PRJ136_W11_2025</t>
   </si>
   <si>
@@ -551,12 +545,12 @@
     <t>PRJ121_W13_2025</t>
   </si>
   <si>
+    <t>PRJ119_W14_2025</t>
+  </si>
+  <si>
     <t>PRJ180_W21_2025</t>
   </si>
   <si>
-    <t>PRJ129_W15_2025</t>
-  </si>
-  <si>
     <t>PRJ193_W18_2025</t>
   </si>
   <si>
@@ -569,18 +563,12 @@
     <t>PRJ109_W13_2025</t>
   </si>
   <si>
-    <t>PRJ131_W14_2025</t>
-  </si>
-  <si>
-    <t>PRJ197_W19_2025</t>
+    <t>PRJ190_W22_2025</t>
   </si>
   <si>
     <t>PRJ117_W20_2025</t>
   </si>
   <si>
-    <t>PRJ190_W22_2025</t>
-  </si>
-  <si>
     <t>PRJ162_W19_2025</t>
   </si>
   <si>
@@ -593,12 +581,12 @@
     <t>PRJ100_W20_2025</t>
   </si>
   <si>
-    <t>PRJ143_W17_2025</t>
-  </si>
-  <si>
     <t>PRJ148_W19_2025</t>
   </si>
   <si>
+    <t>PRJ126_W14_2025</t>
+  </si>
+  <si>
     <t>PRJ151_W22_2025</t>
   </si>
   <si>
@@ -611,7 +599,7 @@
     <t>PRJ147_W23_2025</t>
   </si>
   <si>
-    <t>PRJ107_W15_2025</t>
+    <t>PRJ136_W12_2025</t>
   </si>
   <si>
     <t>PRJ170_W21_2025</t>
@@ -620,6 +608,9 @@
     <t>PRJ134_W16_2025</t>
   </si>
   <si>
+    <t>PRJ183_W11_2025</t>
+  </si>
+  <si>
     <t>PRJ199_W22_2025</t>
   </si>
   <si>
@@ -659,6 +650,9 @@
     <t>PRJ180_W18_2025</t>
   </si>
   <si>
+    <t>PRJ125_W20_2025</t>
+  </si>
+  <si>
     <t>PRJ141_W19_2025</t>
   </si>
   <si>
@@ -668,7 +662,7 @@
     <t>PRJ143_W15_2025</t>
   </si>
   <si>
-    <t>PRJ145_W11_2025</t>
+    <t>PRJ166_W10_2025</t>
   </si>
   <si>
     <t>PRJ159_W16_2025</t>
@@ -677,6 +671,9 @@
     <t>PRJ191_W15_2025</t>
   </si>
   <si>
+    <t>PRJ160_W21_2025</t>
+  </si>
+  <si>
     <t>PRJ188_W13_2025</t>
   </si>
   <si>
@@ -689,6 +686,9 @@
     <t>PRJ194_W19_2025</t>
   </si>
   <si>
+    <t>PRJ124_W21_2025</t>
+  </si>
+  <si>
     <t>PRJ196_W15_2025</t>
   </si>
   <si>
@@ -713,6 +713,9 @@
     <t>PRJ115_W15_2025</t>
   </si>
   <si>
+    <t>PRJ174_W19_2025</t>
+  </si>
+  <si>
     <t>PRJ195_W14_2025</t>
   </si>
   <si>
@@ -731,6 +734,9 @@
     <t>PRJ122_W13_2025</t>
   </si>
   <si>
+    <t>PRJ182_W16_2025</t>
+  </si>
+  <si>
     <t>PRJ108_W16_2025</t>
   </si>
   <si>
@@ -746,12 +752,18 @@
     <t>PRJ134_W21_2025</t>
   </si>
   <si>
+    <t>PRJ190_W21_2025</t>
+  </si>
+  <si>
     <t>PRJ132_W21_2025</t>
   </si>
   <si>
     <t>PRJ167_W14_2025</t>
   </si>
   <si>
+    <t>PRJ137_W21_2025</t>
+  </si>
+  <si>
     <t>PRJ196_W13_2025</t>
   </si>
   <si>
@@ -767,6 +779,9 @@
     <t>PRJ163_W20_2025</t>
   </si>
   <si>
+    <t>PRJ135_W17_2025</t>
+  </si>
+  <si>
     <t>PRJ183_W18_2025</t>
   </si>
   <si>
@@ -776,6 +791,9 @@
     <t>PRJ134_W12_2025</t>
   </si>
   <si>
+    <t>PRJ130_W17_2025</t>
+  </si>
+  <si>
     <t>PRJ120_W19_2025</t>
   </si>
   <si>
@@ -791,9 +809,6 @@
     <t>PRJ140_W21_2025</t>
   </si>
   <si>
-    <t>PRJ171_W20_2025</t>
-  </si>
-  <si>
     <t>PRJ169_W12_2025</t>
   </si>
   <si>
@@ -812,7 +827,7 @@
     <t>PRJ179_W16_2025</t>
   </si>
   <si>
-    <t>PRJ123_W12_2025</t>
+    <t>PRJ154_W14_2025</t>
   </si>
   <si>
     <t>PRJ176_W20_2025</t>
@@ -830,9 +845,6 @@
     <t>PRJ127_W13_2025</t>
   </si>
   <si>
-    <t>PRJ107_W17_2025</t>
-  </si>
-  <si>
     <t>PRJ133_W13_2025</t>
   </si>
   <si>
@@ -842,48 +854,45 @@
     <t>PRJ106_W12_2025</t>
   </si>
   <si>
+    <t>PRJ182_W18_2025</t>
+  </si>
+  <si>
     <t>PRJ193_W15_2025</t>
   </si>
   <si>
     <t>PRJ179_W20_2025</t>
   </si>
   <si>
+    <t>PRJ105_W14_2025</t>
+  </si>
+  <si>
     <t>PRJ139_W13_2025</t>
   </si>
   <si>
-    <t>PRJ112_W18_2025</t>
-  </si>
-  <si>
     <t>PRJ137_W16_2025</t>
   </si>
   <si>
     <t>PRJ106_W11_2025</t>
   </si>
   <si>
-    <t>PRJ163_W19_2025</t>
-  </si>
-  <si>
     <t>PRJ101_W23_2025</t>
   </si>
   <si>
     <t>PRJ140_W20_2025</t>
   </si>
   <si>
-    <t>PRJ182_W17_2025</t>
-  </si>
-  <si>
     <t>PRJ169_W21_2025</t>
   </si>
   <si>
-    <t>PRJ110_W23_2025</t>
-  </si>
-  <si>
     <t>PRJ112_W17_2025</t>
   </si>
   <si>
     <t>PRJ195_W12_2025</t>
   </si>
   <si>
+    <t>PRJ153_W11_2025</t>
+  </si>
+  <si>
     <t>PRJ180_W23_2025</t>
   </si>
   <si>
@@ -902,12 +911,12 @@
     <t>PRJ137_W15_2025</t>
   </si>
   <si>
-    <t>PRJ121_W17_2025</t>
-  </si>
-  <si>
     <t>PRJ125_W12_2025</t>
   </si>
   <si>
+    <t>PRJ166_W12_2025</t>
+  </si>
+  <si>
     <t>PRJ104_W14_2025</t>
   </si>
   <si>
@@ -929,9 +938,6 @@
     <t>PRJ112_W21_2025</t>
   </si>
   <si>
-    <t>PRJ182_W19_2025</t>
-  </si>
-  <si>
     <t>PRJ195_W13_2025</t>
   </si>
   <si>
@@ -944,12 +950,12 @@
     <t>PRJ112_W16_2025</t>
   </si>
   <si>
+    <t>PRJ181_W11_2025</t>
+  </si>
+  <si>
     <t>PRJ108_W23_2025</t>
   </si>
   <si>
-    <t>PRJ191_W20_2025</t>
-  </si>
-  <si>
     <t>PRJ173_W23_2025</t>
   </si>
   <si>
@@ -995,9 +1001,6 @@
     <t>PRJ110_W22_2025</t>
   </si>
   <si>
-    <t>PRJ189_W13_2025</t>
-  </si>
-  <si>
     <t>PRJ164_W14_2025</t>
   </si>
   <si>
@@ -1037,7 +1040,10 @@
     <t>PRJ191_W17_2025</t>
   </si>
   <si>
-    <t>PRJ105_W15_2025</t>
+    <t>PRJ163_W18_2025</t>
+  </si>
+  <si>
+    <t>PRJ122_W18_2025</t>
   </si>
   <si>
     <t>PRJ111_W15_2025</t>
@@ -1052,6 +1058,9 @@
     <t>PRJ188_W20_2025</t>
   </si>
   <si>
+    <t>PRJ121_W16_2025</t>
+  </si>
+  <si>
     <t>PRJ192_W13_2025</t>
   </si>
   <si>
@@ -1071,9 +1080,6 @@
   </si>
   <si>
     <t>PRJ197_W16_2025</t>
-  </si>
-  <si>
-    <t>PRJ166_W11_2025</t>
   </si>
   <si>
     <t>PRJ189_W22_2025</t>
@@ -1133,11 +1139,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B358"/>
+  <dimension ref="A1:B360"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="18.25390625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="18.109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.58984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1177,7 +1183,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>7.64</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="6">
@@ -1185,7 +1191,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>2.25</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="7">
@@ -1193,7 +1199,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>6.65</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="8">
@@ -1201,7 +1207,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>6.31</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="9">
@@ -1209,7 +1215,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>4.89</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="10">
@@ -1217,7 +1223,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>11.8</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="11">
@@ -1225,7 +1231,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>5.76</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="12">
@@ -1233,7 +1239,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>8.65</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="13">
@@ -1241,7 +1247,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>4.22</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="14">
@@ -1249,7 +1255,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>8.09</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="15">
@@ -1257,7 +1263,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="16">
@@ -1265,7 +1271,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>2.35</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="17">
@@ -1273,7 +1279,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>7.44</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="18">
@@ -1281,7 +1287,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>2.52</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="19">
@@ -1289,7 +1295,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>8.42</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="20">
@@ -1297,7 +1303,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>8.73</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="21">
@@ -1305,7 +1311,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>8.44</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="22">
@@ -1313,7 +1319,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>6.49</v>
+        <v>12.629999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1321,7 +1327,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>3.04</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="24">
@@ -1329,7 +1335,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>7.86</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="25">
@@ -1337,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>2.17</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="26">
@@ -1345,7 +1351,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>3.89</v>
+        <v>9.45</v>
       </c>
     </row>
     <row r="27">
@@ -1353,7 +1359,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>3.29</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="28">
@@ -1361,7 +1367,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>6.52</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="29">
@@ -1369,7 +1375,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>9.45</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="30">
@@ -1377,7 +1383,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>9.08</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="31">
@@ -1385,7 +1391,7 @@
         <v>31</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>2.13</v>
+        <v>24.89</v>
       </c>
     </row>
     <row r="32">
@@ -1393,7 +1399,7 @@
         <v>32</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>6.95</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="33">
@@ -1401,7 +1407,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>9.25</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="34">
@@ -1409,7 +1415,7 @@
         <v>34</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>21.96</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="35">
@@ -1417,7 +1423,7 @@
         <v>35</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>3.63</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="36">
@@ -1425,7 +1431,7 @@
         <v>36</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>1.63</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="37">
@@ -1433,7 +1439,7 @@
         <v>37</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>2.95</v>
+        <v>13.35</v>
       </c>
     </row>
     <row r="38">
@@ -1441,7 +1447,7 @@
         <v>38</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>7.54</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="39">
@@ -1449,7 +1455,7 @@
         <v>39</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>2.6</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="40">
@@ -1457,7 +1463,7 @@
         <v>40</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>13.35</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="41">
@@ -1465,7 +1471,7 @@
         <v>41</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>2.79</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="42">
@@ -1473,7 +1479,7 @@
         <v>42</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>7.24</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="43">
@@ -1481,7 +1487,7 @@
         <v>43</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>8.09</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="44">
@@ -1489,7 +1495,7 @@
         <v>44</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>5.06</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="45">
@@ -1497,7 +1503,7 @@
         <v>45</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>5.9</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="46">
@@ -1505,7 +1511,7 @@
         <v>46</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>6.03</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="47">
@@ -1513,7 +1519,7 @@
         <v>47</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>8.98</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="48">
@@ -1521,7 +1527,7 @@
         <v>48</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>15.64</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="49">
@@ -1529,7 +1535,7 @@
         <v>49</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>9.41</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="50">
@@ -1537,7 +1543,7 @@
         <v>50</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>3.74</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="51">
@@ -1545,7 +1551,7 @@
         <v>51</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>8.44</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="52">
@@ -1553,7 +1559,7 @@
         <v>52</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>2.94</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="53">
@@ -1561,7 +1567,7 @@
         <v>53</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>8.26</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="54">
@@ -1569,7 +1575,7 @@
         <v>54</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>3.86</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="55">
@@ -1577,7 +1583,7 @@
         <v>55</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>5.28</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="56">
@@ -1585,7 +1591,7 @@
         <v>56</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>2.52</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="57">
@@ -1593,7 +1599,7 @@
         <v>57</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>3.85</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="58">
@@ -1601,7 +1607,7 @@
         <v>58</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>6.27</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="59">
@@ -1609,7 +1615,7 @@
         <v>59</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>3.65</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="60">
@@ -1617,7 +1623,7 @@
         <v>60</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>4.88</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="61">
@@ -1625,7 +1631,7 @@
         <v>61</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>1.0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="62">
@@ -1633,7 +1639,7 @@
         <v>62</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>8.49</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="63">
@@ -1641,7 +1647,7 @@
         <v>63</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>4.44</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="64">
@@ -1649,7 +1655,7 @@
         <v>64</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>6.74</v>
+        <v>9.39</v>
       </c>
     </row>
     <row r="65">
@@ -1657,7 +1663,7 @@
         <v>65</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>2.2</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="66">
@@ -1665,7 +1671,7 @@
         <v>66</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>7.93</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="67">
@@ -1673,7 +1679,7 @@
         <v>67</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="68">
@@ -1681,7 +1687,7 @@
         <v>68</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>4.7</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="69">
@@ -1689,7 +1695,7 @@
         <v>69</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>9.39</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="70">
@@ -1697,7 +1703,7 @@
         <v>70</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>8.77</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="71">
@@ -1705,7 +1711,7 @@
         <v>71</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>13.02</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="72">
@@ -1713,7 +1719,7 @@
         <v>72</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>6.4</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="73">
@@ -1721,7 +1727,7 @@
         <v>73</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>5.58</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="74">
@@ -1729,7 +1735,7 @@
         <v>74</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>4.53</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="75">
@@ -1737,7 +1743,7 @@
         <v>75</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>1.15</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="76">
@@ -1745,7 +1751,7 @@
         <v>76</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>3.79</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="77">
@@ -1753,7 +1759,7 @@
         <v>77</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>5.01</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="78">
@@ -1761,7 +1767,7 @@
         <v>78</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>8.43</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="79">
@@ -1769,7 +1775,7 @@
         <v>79</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="80">
@@ -1777,7 +1783,7 @@
         <v>80</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>3.33</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="81">
@@ -1785,7 +1791,7 @@
         <v>81</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>7.22</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="82">
@@ -1793,7 +1799,7 @@
         <v>82</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>3.94</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="83">
@@ -1801,7 +1807,7 @@
         <v>83</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>4.3</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="84">
@@ -1809,7 +1815,7 @@
         <v>84</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>8.71</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="85">
@@ -1817,7 +1823,7 @@
         <v>85</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>1.52</v>
+        <v>9.8</v>
       </c>
     </row>
     <row r="86">
@@ -1825,7 +1831,7 @@
         <v>86</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>4.45</v>
+        <v>9.88</v>
       </c>
     </row>
     <row r="87">
@@ -1833,7 +1839,7 @@
         <v>87</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>3.37</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="88">
@@ -1841,7 +1847,7 @@
         <v>88</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>3.86</v>
+        <v>14.48</v>
       </c>
     </row>
     <row r="89">
@@ -1849,7 +1855,7 @@
         <v>89</v>
       </c>
       <c r="B89" t="n" s="0">
-        <v>3.44</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="90">
@@ -1857,7 +1863,7 @@
         <v>90</v>
       </c>
       <c r="B90" t="n" s="0">
-        <v>7.89</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="91">
@@ -1865,7 +1871,7 @@
         <v>91</v>
       </c>
       <c r="B91" t="n" s="0">
-        <v>9.8</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="92">
@@ -1873,7 +1879,7 @@
         <v>92</v>
       </c>
       <c r="B92" t="n" s="0">
-        <v>9.88</v>
+        <v>9.64</v>
       </c>
     </row>
     <row r="93">
@@ -1881,7 +1887,7 @@
         <v>93</v>
       </c>
       <c r="B93" t="n" s="0">
-        <v>7.73</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="94">
@@ -1889,7 +1895,7 @@
         <v>94</v>
       </c>
       <c r="B94" t="n" s="0">
-        <v>7.85</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="95">
@@ -1897,7 +1903,7 @@
         <v>95</v>
       </c>
       <c r="B95" t="n" s="0">
-        <v>8.41</v>
+        <v>8.78</v>
       </c>
     </row>
     <row r="96">
@@ -1905,7 +1911,7 @@
         <v>96</v>
       </c>
       <c r="B96" t="n" s="0">
-        <v>7.87</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="97">
@@ -1913,7 +1919,7 @@
         <v>97</v>
       </c>
       <c r="B97" t="n" s="0">
-        <v>14.54</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="98">
@@ -1921,7 +1927,7 @@
         <v>98</v>
       </c>
       <c r="B98" t="n" s="0">
-        <v>4.85</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="99">
@@ -1929,7 +1935,7 @@
         <v>99</v>
       </c>
       <c r="B99" t="n" s="0">
-        <v>1.02</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="100">
@@ -1937,7 +1943,7 @@
         <v>100</v>
       </c>
       <c r="B100" t="n" s="0">
-        <v>9.64</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="101">
@@ -1945,7 +1951,7 @@
         <v>101</v>
       </c>
       <c r="B101" t="n" s="0">
-        <v>7.88</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="102">
@@ -1953,7 +1959,7 @@
         <v>102</v>
       </c>
       <c r="B102" t="n" s="0">
-        <v>8.78</v>
+        <v>9.71</v>
       </c>
     </row>
     <row r="103">
@@ -1961,7 +1967,7 @@
         <v>103</v>
       </c>
       <c r="B103" t="n" s="0">
-        <v>4.97</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="104">
@@ -1969,7 +1975,7 @@
         <v>104</v>
       </c>
       <c r="B104" t="n" s="0">
-        <v>8.28</v>
+        <v>6.34</v>
       </c>
     </row>
     <row r="105">
@@ -1977,7 +1983,7 @@
         <v>105</v>
       </c>
       <c r="B105" t="n" s="0">
-        <v>13.17</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="106">
@@ -1985,7 +1991,7 @@
         <v>106</v>
       </c>
       <c r="B106" t="n" s="0">
-        <v>10.04</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="107">
@@ -1993,7 +1999,7 @@
         <v>107</v>
       </c>
       <c r="B107" t="n" s="0">
-        <v>2.61</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="108">
@@ -2001,7 +2007,7 @@
         <v>108</v>
       </c>
       <c r="B108" t="n" s="0">
-        <v>5.12</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="109">
@@ -2009,7 +2015,7 @@
         <v>109</v>
       </c>
       <c r="B109" t="n" s="0">
-        <v>4.93</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="110">
@@ -2017,7 +2023,7 @@
         <v>110</v>
       </c>
       <c r="B110" t="n" s="0">
-        <v>3.3</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="111">
@@ -2025,7 +2031,7 @@
         <v>111</v>
       </c>
       <c r="B111" t="n" s="0">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="112">
@@ -2033,7 +2039,7 @@
         <v>112</v>
       </c>
       <c r="B112" t="n" s="0">
-        <v>9.71</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="113">
@@ -2041,7 +2047,7 @@
         <v>113</v>
       </c>
       <c r="B113" t="n" s="0">
-        <v>3.9</v>
+        <v>9.29</v>
       </c>
     </row>
     <row r="114">
@@ -2049,7 +2055,7 @@
         <v>114</v>
       </c>
       <c r="B114" t="n" s="0">
-        <v>6.34</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="115">
@@ -2057,7 +2063,7 @@
         <v>115</v>
       </c>
       <c r="B115" t="n" s="0">
-        <v>11.32</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="116">
@@ -2065,7 +2071,7 @@
         <v>116</v>
       </c>
       <c r="B116" t="n" s="0">
-        <v>1.49</v>
+        <v>9.13</v>
       </c>
     </row>
     <row r="117">
@@ -2073,7 +2079,7 @@
         <v>117</v>
       </c>
       <c r="B117" t="n" s="0">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="118">
@@ -2081,7 +2087,7 @@
         <v>118</v>
       </c>
       <c r="B118" t="n" s="0">
-        <v>1.26</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="119">
@@ -2089,7 +2095,7 @@
         <v>119</v>
       </c>
       <c r="B119" t="n" s="0">
-        <v>12.34</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="120">
@@ -2097,7 +2103,7 @@
         <v>120</v>
       </c>
       <c r="B120" t="n" s="0">
-        <v>1.01</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="121">
@@ -2105,7 +2111,7 @@
         <v>121</v>
       </c>
       <c r="B121" t="n" s="0">
-        <v>5.09</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="122">
@@ -2113,7 +2119,7 @@
         <v>122</v>
       </c>
       <c r="B122" t="n" s="0">
-        <v>9.13</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="123">
@@ -2121,7 +2127,7 @@
         <v>123</v>
       </c>
       <c r="B123" t="n" s="0">
-        <v>7.1</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="124">
@@ -2129,7 +2135,7 @@
         <v>124</v>
       </c>
       <c r="B124" t="n" s="0">
-        <v>2.51</v>
+        <v>9.47</v>
       </c>
     </row>
     <row r="125">
@@ -2137,7 +2143,7 @@
         <v>125</v>
       </c>
       <c r="B125" t="n" s="0">
-        <v>7.32</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="126">
@@ -2145,7 +2151,7 @@
         <v>126</v>
       </c>
       <c r="B126" t="n" s="0">
-        <v>3.0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="127">
@@ -2153,7 +2159,7 @@
         <v>127</v>
       </c>
       <c r="B127" t="n" s="0">
-        <v>2.28</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="128">
@@ -2161,7 +2167,7 @@
         <v>128</v>
       </c>
       <c r="B128" t="n" s="0">
-        <v>6.88</v>
+        <v>8.71</v>
       </c>
     </row>
     <row r="129">
@@ -2169,7 +2175,7 @@
         <v>129</v>
       </c>
       <c r="B129" t="n" s="0">
-        <v>5.51</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="130">
@@ -2177,7 +2183,7 @@
         <v>130</v>
       </c>
       <c r="B130" t="n" s="0">
-        <v>6.74</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="131">
@@ -2185,7 +2191,7 @@
         <v>131</v>
       </c>
       <c r="B131" t="n" s="0">
-        <v>9.47</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="132">
@@ -2193,7 +2199,7 @@
         <v>132</v>
       </c>
       <c r="B132" t="n" s="0">
-        <v>10.45</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="133">
@@ -2201,7 +2207,7 @@
         <v>133</v>
       </c>
       <c r="B133" t="n" s="0">
-        <v>2.78</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="134">
@@ -2209,7 +2215,7 @@
         <v>134</v>
       </c>
       <c r="B134" t="n" s="0">
-        <v>3.34</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="135">
@@ -2217,7 +2223,7 @@
         <v>135</v>
       </c>
       <c r="B135" t="n" s="0">
-        <v>7.71</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="136">
@@ -2225,7 +2231,7 @@
         <v>136</v>
       </c>
       <c r="B136" t="n" s="0">
-        <v>1.39</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="137">
@@ -2233,7 +2239,7 @@
         <v>137</v>
       </c>
       <c r="B137" t="n" s="0">
-        <v>3.76</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="138">
@@ -2241,7 +2247,7 @@
         <v>138</v>
       </c>
       <c r="B138" t="n" s="0">
-        <v>1.56</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="139">
@@ -2249,7 +2255,7 @@
         <v>139</v>
       </c>
       <c r="B139" t="n" s="0">
-        <v>3.95</v>
+        <v>9.46</v>
       </c>
     </row>
     <row r="140">
@@ -2257,7 +2263,7 @@
         <v>140</v>
       </c>
       <c r="B140" t="n" s="0">
-        <v>8.6</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="141">
@@ -2265,7 +2271,7 @@
         <v>141</v>
       </c>
       <c r="B141" t="n" s="0">
-        <v>4.87</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="142">
@@ -2273,7 +2279,7 @@
         <v>142</v>
       </c>
       <c r="B142" t="n" s="0">
-        <v>9.850000000000001</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="143">
@@ -2281,7 +2287,7 @@
         <v>143</v>
       </c>
       <c r="B143" t="n" s="0">
-        <v>6.37</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="144">
@@ -2289,7 +2295,7 @@
         <v>144</v>
       </c>
       <c r="B144" t="n" s="0">
-        <v>9.46</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="145">
@@ -2297,7 +2303,7 @@
         <v>145</v>
       </c>
       <c r="B145" t="n" s="0">
-        <v>1.93</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="146">
@@ -2305,7 +2311,7 @@
         <v>146</v>
       </c>
       <c r="B146" t="n" s="0">
-        <v>7.46</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="147">
@@ -2313,7 +2319,7 @@
         <v>147</v>
       </c>
       <c r="B147" t="n" s="0">
-        <v>4.11</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="148">
@@ -2321,7 +2327,7 @@
         <v>148</v>
       </c>
       <c r="B148" t="n" s="0">
-        <v>4.51</v>
+        <v>9.03</v>
       </c>
     </row>
     <row r="149">
@@ -2329,7 +2335,7 @@
         <v>149</v>
       </c>
       <c r="B149" t="n" s="0">
-        <v>4.04</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="150">
@@ -2337,7 +2343,7 @@
         <v>150</v>
       </c>
       <c r="B150" t="n" s="0">
-        <v>9.6</v>
+        <v>8.54</v>
       </c>
     </row>
     <row r="151">
@@ -2345,7 +2351,7 @@
         <v>151</v>
       </c>
       <c r="B151" t="n" s="0">
-        <v>5.45</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="152">
@@ -2353,7 +2359,7 @@
         <v>152</v>
       </c>
       <c r="B152" t="n" s="0">
-        <v>1.32</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="153">
@@ -2361,7 +2367,7 @@
         <v>153</v>
       </c>
       <c r="B153" t="n" s="0">
-        <v>1.6</v>
+        <v>8.37</v>
       </c>
     </row>
     <row r="154">
@@ -2369,7 +2375,7 @@
         <v>154</v>
       </c>
       <c r="B154" t="n" s="0">
-        <v>9.03</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="155">
@@ -2377,7 +2383,7 @@
         <v>155</v>
       </c>
       <c r="B155" t="n" s="0">
-        <v>8.54</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="156">
@@ -2385,7 +2391,7 @@
         <v>156</v>
       </c>
       <c r="B156" t="n" s="0">
-        <v>4.03</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="157">
@@ -2393,7 +2399,7 @@
         <v>157</v>
       </c>
       <c r="B157" t="n" s="0">
-        <v>8.37</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="158">
@@ -2401,7 +2407,7 @@
         <v>158</v>
       </c>
       <c r="B158" t="n" s="0">
-        <v>9.2</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="159">
@@ -2409,7 +2415,7 @@
         <v>159</v>
       </c>
       <c r="B159" t="n" s="0">
-        <v>2.93</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="160">
@@ -2417,7 +2423,7 @@
         <v>160</v>
       </c>
       <c r="B160" t="n" s="0">
-        <v>3.68</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="161">
@@ -2425,7 +2431,7 @@
         <v>161</v>
       </c>
       <c r="B161" t="n" s="0">
-        <v>11.36</v>
+        <v>9.71</v>
       </c>
     </row>
     <row r="162">
@@ -2433,7 +2439,7 @@
         <v>162</v>
       </c>
       <c r="B162" t="n" s="0">
-        <v>9.71</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="163">
@@ -2441,7 +2447,7 @@
         <v>163</v>
       </c>
       <c r="B163" t="n" s="0">
-        <v>5.29</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="164">
@@ -2449,7 +2455,7 @@
         <v>164</v>
       </c>
       <c r="B164" t="n" s="0">
-        <v>6.34</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="165">
@@ -2465,7 +2471,7 @@
         <v>166</v>
       </c>
       <c r="B166" t="n" s="0">
-        <v>3.06</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="167">
@@ -2473,7 +2479,7 @@
         <v>167</v>
       </c>
       <c r="B167" t="n" s="0">
-        <v>4.6</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="168">
@@ -2481,7 +2487,7 @@
         <v>168</v>
       </c>
       <c r="B168" t="n" s="0">
-        <v>3.36</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="169">
@@ -2489,7 +2495,7 @@
         <v>169</v>
       </c>
       <c r="B169" t="n" s="0">
-        <v>8.3</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="170">
@@ -2497,7 +2503,7 @@
         <v>170</v>
       </c>
       <c r="B170" t="n" s="0">
-        <v>2.38</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="171">
@@ -2505,7 +2511,7 @@
         <v>171</v>
       </c>
       <c r="B171" t="n" s="0">
-        <v>3.89</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="172">
@@ -2513,7 +2519,7 @@
         <v>172</v>
       </c>
       <c r="B172" t="n" s="0">
-        <v>1.59</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="173">
@@ -2521,7 +2527,7 @@
         <v>173</v>
       </c>
       <c r="B173" t="n" s="0">
-        <v>1.05</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="174">
@@ -2529,7 +2535,7 @@
         <v>174</v>
       </c>
       <c r="B174" t="n" s="0">
-        <v>5.0</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="175">
@@ -2537,7 +2543,7 @@
         <v>175</v>
       </c>
       <c r="B175" t="n" s="0">
-        <v>4.0</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="176">
@@ -2545,7 +2551,7 @@
         <v>176</v>
       </c>
       <c r="B176" t="n" s="0">
-        <v>5.72</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="177">
@@ -2553,7 +2559,7 @@
         <v>177</v>
       </c>
       <c r="B177" t="n" s="0">
-        <v>8.93</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="178">
@@ -2561,7 +2567,7 @@
         <v>178</v>
       </c>
       <c r="B178" t="n" s="0">
-        <v>4.55</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="179">
@@ -2569,7 +2575,7 @@
         <v>179</v>
       </c>
       <c r="B179" t="n" s="0">
-        <v>6.4</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="180">
@@ -2577,7 +2583,7 @@
         <v>180</v>
       </c>
       <c r="B180" t="n" s="0">
-        <v>6.4</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="181">
@@ -2585,7 +2591,7 @@
         <v>181</v>
       </c>
       <c r="B181" t="n" s="0">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="182">
@@ -2593,7 +2599,7 @@
         <v>182</v>
       </c>
       <c r="B182" t="n" s="0">
-        <v>3.05</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="183">
@@ -2601,7 +2607,7 @@
         <v>183</v>
       </c>
       <c r="B183" t="n" s="0">
-        <v>1.42</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="184">
@@ -2609,7 +2615,7 @@
         <v>184</v>
       </c>
       <c r="B184" t="n" s="0">
-        <v>1.91</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="185">
@@ -2617,7 +2623,7 @@
         <v>185</v>
       </c>
       <c r="B185" t="n" s="0">
-        <v>5.9</v>
+        <v>9.88</v>
       </c>
     </row>
     <row r="186">
@@ -2625,7 +2631,7 @@
         <v>186</v>
       </c>
       <c r="B186" t="n" s="0">
-        <v>1.75</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="187">
@@ -2633,7 +2639,7 @@
         <v>187</v>
       </c>
       <c r="B187" t="n" s="0">
-        <v>1.09</v>
+        <v>8.39</v>
       </c>
     </row>
     <row r="188">
@@ -2641,7 +2647,7 @@
         <v>188</v>
       </c>
       <c r="B188" t="n" s="0">
-        <v>13.8</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="189">
@@ -2649,7 +2655,7 @@
         <v>189</v>
       </c>
       <c r="B189" t="n" s="0">
-        <v>9.88</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="190">
@@ -2657,7 +2663,7 @@
         <v>190</v>
       </c>
       <c r="B190" t="n" s="0">
-        <v>6.0</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="191">
@@ -2665,7 +2671,7 @@
         <v>191</v>
       </c>
       <c r="B191" t="n" s="0">
-        <v>8.39</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="192">
@@ -2673,7 +2679,7 @@
         <v>192</v>
       </c>
       <c r="B192" t="n" s="0">
-        <v>3.08</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="193">
@@ -2681,7 +2687,7 @@
         <v>193</v>
       </c>
       <c r="B193" t="n" s="0">
-        <v>4.77</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="194">
@@ -2689,7 +2695,7 @@
         <v>194</v>
       </c>
       <c r="B194" t="n" s="0">
-        <v>8.52</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="195">
@@ -2697,7 +2703,7 @@
         <v>195</v>
       </c>
       <c r="B195" t="n" s="0">
-        <v>5.52</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="196">
@@ -2705,7 +2711,7 @@
         <v>196</v>
       </c>
       <c r="B196" t="n" s="0">
-        <v>8.19</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="197">
@@ -2713,7 +2719,7 @@
         <v>197</v>
       </c>
       <c r="B197" t="n" s="0">
-        <v>3.88</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="198">
@@ -2721,7 +2727,7 @@
         <v>198</v>
       </c>
       <c r="B198" t="n" s="0">
-        <v>3.19</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="199">
@@ -2729,7 +2735,7 @@
         <v>199</v>
       </c>
       <c r="B199" t="n" s="0">
-        <v>1.16</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="200">
@@ -2737,7 +2743,7 @@
         <v>200</v>
       </c>
       <c r="B200" t="n" s="0">
-        <v>2.97</v>
+        <v>8.05</v>
       </c>
     </row>
     <row r="201">
@@ -2745,7 +2751,7 @@
         <v>201</v>
       </c>
       <c r="B201" t="n" s="0">
-        <v>1.4</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="202">
@@ -2753,7 +2759,7 @@
         <v>202</v>
       </c>
       <c r="B202" t="n" s="0">
-        <v>3.09</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="203">
@@ -2761,7 +2767,7 @@
         <v>203</v>
       </c>
       <c r="B203" t="n" s="0">
-        <v>8.05</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="204">
@@ -2769,7 +2775,7 @@
         <v>204</v>
       </c>
       <c r="B204" t="n" s="0">
-        <v>4.87</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="205">
@@ -2777,7 +2783,7 @@
         <v>205</v>
       </c>
       <c r="B205" t="n" s="0">
-        <v>8.19</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="206">
@@ -2785,7 +2791,7 @@
         <v>206</v>
       </c>
       <c r="B206" t="n" s="0">
-        <v>1.09</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="207">
@@ -2793,7 +2799,7 @@
         <v>207</v>
       </c>
       <c r="B207" t="n" s="0">
-        <v>5.58</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="208">
@@ -2801,7 +2807,7 @@
         <v>208</v>
       </c>
       <c r="B208" t="n" s="0">
-        <v>6.36</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="209">
@@ -2809,7 +2815,7 @@
         <v>209</v>
       </c>
       <c r="B209" t="n" s="0">
-        <v>1.89</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="210">
@@ -2817,7 +2823,7 @@
         <v>210</v>
       </c>
       <c r="B210" t="n" s="0">
-        <v>9.15</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="211">
@@ -2825,7 +2831,7 @@
         <v>211</v>
       </c>
       <c r="B211" t="n" s="0">
-        <v>4.42</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="212">
@@ -2833,7 +2839,7 @@
         <v>212</v>
       </c>
       <c r="B212" t="n" s="0">
-        <v>8.56</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="213">
@@ -2841,7 +2847,7 @@
         <v>213</v>
       </c>
       <c r="B213" t="n" s="0">
-        <v>2.72</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="214">
@@ -2849,7 +2855,7 @@
         <v>214</v>
       </c>
       <c r="B214" t="n" s="0">
-        <v>5.63</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="215">
@@ -2857,7 +2863,7 @@
         <v>215</v>
       </c>
       <c r="B215" t="n" s="0">
-        <v>2.08</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="216">
@@ -2865,7 +2871,7 @@
         <v>216</v>
       </c>
       <c r="B216" t="n" s="0">
-        <v>2.22</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="217">
@@ -2873,7 +2879,7 @@
         <v>217</v>
       </c>
       <c r="B217" t="n" s="0">
-        <v>11.350000000000001</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="218">
@@ -2881,7 +2887,7 @@
         <v>218</v>
       </c>
       <c r="B218" t="n" s="0">
-        <v>1.57</v>
+        <v>8.04</v>
       </c>
     </row>
     <row r="219">
@@ -2889,7 +2895,7 @@
         <v>219</v>
       </c>
       <c r="B219" t="n" s="0">
-        <v>2.58</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="220">
@@ -2897,7 +2903,7 @@
         <v>220</v>
       </c>
       <c r="B220" t="n" s="0">
-        <v>3.16</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="221">
@@ -2905,7 +2911,7 @@
         <v>221</v>
       </c>
       <c r="B221" t="n" s="0">
-        <v>5.28</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="222">
@@ -2913,7 +2919,7 @@
         <v>222</v>
       </c>
       <c r="B222" t="n" s="0">
-        <v>6.18</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="223">
@@ -2921,7 +2927,7 @@
         <v>223</v>
       </c>
       <c r="B223" t="n" s="0">
-        <v>7.74</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="224">
@@ -2929,7 +2935,7 @@
         <v>224</v>
       </c>
       <c r="B224" t="n" s="0">
-        <v>8.91</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="225">
@@ -3001,7 +3007,7 @@
         <v>233</v>
       </c>
       <c r="B233" t="n" s="0">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="234">
@@ -3009,7 +3015,7 @@
         <v>234</v>
       </c>
       <c r="B234" t="n" s="0">
-        <v>7.67</v>
+        <v>6.6899999999999995</v>
       </c>
     </row>
     <row r="235">
@@ -3017,7 +3023,7 @@
         <v>235</v>
       </c>
       <c r="B235" t="n" s="0">
-        <v>2.78</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="236">
@@ -3025,7 +3031,7 @@
         <v>236</v>
       </c>
       <c r="B236" t="n" s="0">
-        <v>6.99</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="237">
@@ -3033,7 +3039,7 @@
         <v>237</v>
       </c>
       <c r="B237" t="n" s="0">
-        <v>1.87</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="238">
@@ -3041,7 +3047,7 @@
         <v>238</v>
       </c>
       <c r="B238" t="n" s="0">
-        <v>4.6</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="239">
@@ -3049,7 +3055,7 @@
         <v>239</v>
       </c>
       <c r="B239" t="n" s="0">
-        <v>10.0</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="240">
@@ -3057,7 +3063,7 @@
         <v>240</v>
       </c>
       <c r="B240" t="n" s="0">
-        <v>8.77</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="241">
@@ -3065,7 +3071,7 @@
         <v>241</v>
       </c>
       <c r="B241" t="n" s="0">
-        <v>3.03</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="242">
@@ -3073,7 +3079,7 @@
         <v>242</v>
       </c>
       <c r="B242" t="n" s="0">
-        <v>6.66</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="243">
@@ -3081,7 +3087,7 @@
         <v>243</v>
       </c>
       <c r="B243" t="n" s="0">
-        <v>8.45</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="244">
@@ -3089,7 +3095,7 @@
         <v>244</v>
       </c>
       <c r="B244" t="n" s="0">
-        <v>5.19</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="245">
@@ -3097,7 +3103,7 @@
         <v>245</v>
       </c>
       <c r="B245" t="n" s="0">
-        <v>9.33</v>
+        <v>8.45</v>
       </c>
     </row>
     <row r="246">
@@ -3105,7 +3111,7 @@
         <v>246</v>
       </c>
       <c r="B246" t="n" s="0">
-        <v>1.15</v>
+        <v>9.05</v>
       </c>
     </row>
     <row r="247">
@@ -3113,7 +3119,7 @@
         <v>247</v>
       </c>
       <c r="B247" t="n" s="0">
-        <v>7.52</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="248">
@@ -3121,7 +3127,7 @@
         <v>248</v>
       </c>
       <c r="B248" t="n" s="0">
-        <v>2.31</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="249">
@@ -3129,7 +3135,7 @@
         <v>249</v>
       </c>
       <c r="B249" t="n" s="0">
-        <v>15.55</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="250">
@@ -3137,7 +3143,7 @@
         <v>250</v>
       </c>
       <c r="B250" t="n" s="0">
-        <v>3.58</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="251">
@@ -3145,7 +3151,7 @@
         <v>251</v>
       </c>
       <c r="B251" t="n" s="0">
-        <v>5.84</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="252">
@@ -3153,7 +3159,7 @@
         <v>252</v>
       </c>
       <c r="B252" t="n" s="0">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="253">
@@ -3161,7 +3167,7 @@
         <v>253</v>
       </c>
       <c r="B253" t="n" s="0">
-        <v>6.4</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="254">
@@ -3169,7 +3175,7 @@
         <v>254</v>
       </c>
       <c r="B254" t="n" s="0">
-        <v>9.34</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="255">
@@ -3177,7 +3183,7 @@
         <v>255</v>
       </c>
       <c r="B255" t="n" s="0">
-        <v>7.43</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="256">
@@ -3185,7 +3191,7 @@
         <v>256</v>
       </c>
       <c r="B256" t="n" s="0">
-        <v>8.76</v>
+        <v>9.7</v>
       </c>
     </row>
     <row r="257">
@@ -3193,7 +3199,7 @@
         <v>257</v>
       </c>
       <c r="B257" t="n" s="0">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="258">
@@ -3201,7 +3207,7 @@
         <v>258</v>
       </c>
       <c r="B258" t="n" s="0">
-        <v>7.88</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="259">
@@ -3209,7 +3215,7 @@
         <v>259</v>
       </c>
       <c r="B259" t="n" s="0">
-        <v>8.08</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="260">
@@ -3217,7 +3223,7 @@
         <v>260</v>
       </c>
       <c r="B260" t="n" s="0">
-        <v>8.44</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="261">
@@ -3225,7 +3231,7 @@
         <v>261</v>
       </c>
       <c r="B261" t="n" s="0">
-        <v>4.44</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="262">
@@ -3233,7 +3239,7 @@
         <v>262</v>
       </c>
       <c r="B262" t="n" s="0">
-        <v>8.5</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="263">
@@ -3241,7 +3247,7 @@
         <v>263</v>
       </c>
       <c r="B263" t="n" s="0">
-        <v>4.15</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="264">
@@ -3249,7 +3255,7 @@
         <v>264</v>
       </c>
       <c r="B264" t="n" s="0">
-        <v>8.73</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="265">
@@ -3257,7 +3263,7 @@
         <v>265</v>
       </c>
       <c r="B265" t="n" s="0">
-        <v>9.719999999999999</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="266">
@@ -3265,7 +3271,7 @@
         <v>266</v>
       </c>
       <c r="B266" t="n" s="0">
-        <v>3.47</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="267">
@@ -3273,7 +3279,7 @@
         <v>267</v>
       </c>
       <c r="B267" t="n" s="0">
-        <v>1.18</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="268">
@@ -3281,7 +3287,7 @@
         <v>268</v>
       </c>
       <c r="B268" t="n" s="0">
-        <v>1.11</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="269">
@@ -3289,7 +3295,7 @@
         <v>269</v>
       </c>
       <c r="B269" t="n" s="0">
-        <v>2.48</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="270">
@@ -3297,7 +3303,7 @@
         <v>270</v>
       </c>
       <c r="B270" t="n" s="0">
-        <v>10.91</v>
+        <v>9.719999999999999</v>
       </c>
     </row>
     <row r="271">
@@ -3305,7 +3311,7 @@
         <v>271</v>
       </c>
       <c r="B271" t="n" s="0">
-        <v>1.87</v>
+        <v>6.34</v>
       </c>
     </row>
     <row r="272">
@@ -3313,7 +3319,7 @@
         <v>272</v>
       </c>
       <c r="B272" t="n" s="0">
-        <v>9.66</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="273">
@@ -3321,7 +3327,7 @@
         <v>273</v>
       </c>
       <c r="B273" t="n" s="0">
-        <v>4.24</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="274">
@@ -3329,7 +3335,7 @@
         <v>274</v>
       </c>
       <c r="B274" t="n" s="0">
-        <v>9.35</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="275">
@@ -3337,7 +3343,7 @@
         <v>275</v>
       </c>
       <c r="B275" t="n" s="0">
-        <v>7.05</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="276">
@@ -3345,7 +3351,7 @@
         <v>276</v>
       </c>
       <c r="B276" t="n" s="0">
-        <v>1.06</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="277">
@@ -3353,7 +3359,7 @@
         <v>277</v>
       </c>
       <c r="B277" t="n" s="0">
-        <v>3.73</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="278">
@@ -3361,7 +3367,7 @@
         <v>278</v>
       </c>
       <c r="B278" t="n" s="0">
-        <v>15.879999999999997</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="279">
@@ -3369,7 +3375,7 @@
         <v>279</v>
       </c>
       <c r="B279" t="n" s="0">
-        <v>5.18</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="280">
@@ -3377,7 +3383,7 @@
         <v>280</v>
       </c>
       <c r="B280" t="n" s="0">
-        <v>5.11</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="281">
@@ -3385,7 +3391,7 @@
         <v>281</v>
       </c>
       <c r="B281" t="n" s="0">
-        <v>6.23</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="282">
@@ -3393,7 +3399,7 @@
         <v>282</v>
       </c>
       <c r="B282" t="n" s="0">
-        <v>8.85</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="283">
@@ -3401,7 +3407,7 @@
         <v>283</v>
       </c>
       <c r="B283" t="n" s="0">
-        <v>1.81</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="284">
@@ -3409,7 +3415,7 @@
         <v>284</v>
       </c>
       <c r="B284" t="n" s="0">
-        <v>7.79</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="285">
@@ -3417,7 +3423,7 @@
         <v>285</v>
       </c>
       <c r="B285" t="n" s="0">
-        <v>3.41</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="286">
@@ -3425,7 +3431,7 @@
         <v>286</v>
       </c>
       <c r="B286" t="n" s="0">
-        <v>7.24</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="287">
@@ -3433,7 +3439,7 @@
         <v>287</v>
       </c>
       <c r="B287" t="n" s="0">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="288">
@@ -3441,7 +3447,7 @@
         <v>288</v>
       </c>
       <c r="B288" t="n" s="0">
-        <v>6.04</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="289">
@@ -3449,7 +3455,7 @@
         <v>289</v>
       </c>
       <c r="B289" t="n" s="0">
-        <v>6.55</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="290">
@@ -3457,7 +3463,7 @@
         <v>290</v>
       </c>
       <c r="B290" t="n" s="0">
-        <v>2.12</v>
+        <v>11.219999999999999</v>
       </c>
     </row>
     <row r="291">
@@ -3465,7 +3471,7 @@
         <v>291</v>
       </c>
       <c r="B291" t="n" s="0">
-        <v>1.9</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="292">
@@ -3473,7 +3479,7 @@
         <v>292</v>
       </c>
       <c r="B292" t="n" s="0">
-        <v>2.92</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="293">
@@ -3481,7 +3487,7 @@
         <v>293</v>
       </c>
       <c r="B293" t="n" s="0">
-        <v>6.15</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="294">
@@ -3489,7 +3495,7 @@
         <v>294</v>
       </c>
       <c r="B294" t="n" s="0">
-        <v>1.37</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="295">
@@ -3497,7 +3503,7 @@
         <v>295</v>
       </c>
       <c r="B295" t="n" s="0">
-        <v>7.82</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="296">
@@ -3505,7 +3511,7 @@
         <v>296</v>
       </c>
       <c r="B296" t="n" s="0">
-        <v>3.21</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="297">
@@ -3513,7 +3519,7 @@
         <v>297</v>
       </c>
       <c r="B297" t="n" s="0">
-        <v>6.72</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="298">
@@ -3521,7 +3527,7 @@
         <v>298</v>
       </c>
       <c r="B298" t="n" s="0">
-        <v>1.94</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="299">
@@ -3529,7 +3535,7 @@
         <v>299</v>
       </c>
       <c r="B299" t="n" s="0">
-        <v>4.24</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="300">
@@ -3537,7 +3543,7 @@
         <v>300</v>
       </c>
       <c r="B300" t="n" s="0">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="301">
@@ -3545,7 +3551,7 @@
         <v>301</v>
       </c>
       <c r="B301" t="n" s="0">
-        <v>8.28</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="302">
@@ -3553,7 +3559,7 @@
         <v>302</v>
       </c>
       <c r="B302" t="n" s="0">
-        <v>7.2</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="303">
@@ -3561,7 +3567,7 @@
         <v>303</v>
       </c>
       <c r="B303" t="n" s="0">
-        <v>4.67</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="304">
@@ -3569,7 +3575,7 @@
         <v>304</v>
       </c>
       <c r="B304" t="n" s="0">
-        <v>3.32</v>
+        <v>8.28</v>
       </c>
     </row>
     <row r="305">
@@ -3577,7 +3583,7 @@
         <v>305</v>
       </c>
       <c r="B305" t="n" s="0">
-        <v>2.31</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="306">
@@ -3585,7 +3591,7 @@
         <v>306</v>
       </c>
       <c r="B306" t="n" s="0">
-        <v>6.62</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="307">
@@ -3593,7 +3599,7 @@
         <v>307</v>
       </c>
       <c r="B307" t="n" s="0">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="308">
@@ -3601,7 +3607,7 @@
         <v>308</v>
       </c>
       <c r="B308" t="n" s="0">
-        <v>8.11</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="309">
@@ -3609,7 +3615,7 @@
         <v>309</v>
       </c>
       <c r="B309" t="n" s="0">
-        <v>9.29</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="310">
@@ -3617,7 +3623,7 @@
         <v>310</v>
       </c>
       <c r="B310" t="n" s="0">
-        <v>15.66</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="311">
@@ -3625,7 +3631,7 @@
         <v>311</v>
       </c>
       <c r="B311" t="n" s="0">
-        <v>6.63</v>
+        <v>9.29</v>
       </c>
     </row>
     <row r="312">
@@ -3633,7 +3639,7 @@
         <v>312</v>
       </c>
       <c r="B312" t="n" s="0">
-        <v>5.16</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="313">
@@ -3641,7 +3647,7 @@
         <v>313</v>
       </c>
       <c r="B313" t="n" s="0">
-        <v>3.04</v>
+        <v>15.66</v>
       </c>
     </row>
     <row r="314">
@@ -3649,7 +3655,7 @@
         <v>314</v>
       </c>
       <c r="B314" t="n" s="0">
-        <v>7.3</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="315">
@@ -3657,7 +3663,7 @@
         <v>315</v>
       </c>
       <c r="B315" t="n" s="0">
-        <v>7.86</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="316">
@@ -3665,7 +3671,7 @@
         <v>316</v>
       </c>
       <c r="B316" t="n" s="0">
-        <v>1.48</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="317">
@@ -3673,7 +3679,7 @@
         <v>317</v>
       </c>
       <c r="B317" t="n" s="0">
-        <v>3.32</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="318">
@@ -3681,7 +3687,7 @@
         <v>318</v>
       </c>
       <c r="B318" t="n" s="0">
-        <v>3.43</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="319">
@@ -3689,7 +3695,7 @@
         <v>319</v>
       </c>
       <c r="B319" t="n" s="0">
-        <v>8.58</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="320">
@@ -3697,7 +3703,7 @@
         <v>320</v>
       </c>
       <c r="B320" t="n" s="0">
-        <v>2.88</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="321">
@@ -3705,7 +3711,7 @@
         <v>321</v>
       </c>
       <c r="B321" t="n" s="0">
-        <v>2.58</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="322">
@@ -3713,7 +3719,7 @@
         <v>322</v>
       </c>
       <c r="B322" t="n" s="0">
-        <v>11.09</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="323">
@@ -3721,7 +3727,7 @@
         <v>323</v>
       </c>
       <c r="B323" t="n" s="0">
-        <v>5.97</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="324">
@@ -3729,7 +3735,7 @@
         <v>324</v>
       </c>
       <c r="B324" t="n" s="0">
-        <v>6.35</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="325">
@@ -3737,7 +3743,7 @@
         <v>325</v>
       </c>
       <c r="B325" t="n" s="0">
-        <v>9.36</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="326">
@@ -3745,7 +3751,7 @@
         <v>326</v>
       </c>
       <c r="B326" t="n" s="0">
-        <v>5.03</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="327">
@@ -3753,7 +3759,7 @@
         <v>327</v>
       </c>
       <c r="B327" t="n" s="0">
-        <v>3.58</v>
+        <v>9.36</v>
       </c>
     </row>
     <row r="328">
@@ -3761,7 +3767,7 @@
         <v>328</v>
       </c>
       <c r="B328" t="n" s="0">
-        <v>11.209999999999999</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="329">
@@ -3769,7 +3775,7 @@
         <v>329</v>
       </c>
       <c r="B329" t="n" s="0">
-        <v>1.23</v>
+        <v>11.209999999999999</v>
       </c>
     </row>
     <row r="330">
@@ -3777,7 +3783,7 @@
         <v>330</v>
       </c>
       <c r="B330" t="n" s="0">
-        <v>8.52</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="331">
@@ -3785,7 +3791,7 @@
         <v>331</v>
       </c>
       <c r="B331" t="n" s="0">
-        <v>5.44</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="332">
@@ -3793,7 +3799,7 @@
         <v>332</v>
       </c>
       <c r="B332" t="n" s="0">
-        <v>7.14</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="333">
@@ -3801,7 +3807,7 @@
         <v>333</v>
       </c>
       <c r="B333" t="n" s="0">
-        <v>8.17</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="334">
@@ -3809,7 +3815,7 @@
         <v>334</v>
       </c>
       <c r="B334" t="n" s="0">
-        <v>6.09</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="335">
@@ -3817,7 +3823,7 @@
         <v>335</v>
       </c>
       <c r="B335" t="n" s="0">
-        <v>1.18</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="336">
@@ -3825,7 +3831,7 @@
         <v>336</v>
       </c>
       <c r="B336" t="n" s="0">
-        <v>2.16</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="337">
@@ -3833,7 +3839,7 @@
         <v>337</v>
       </c>
       <c r="B337" t="n" s="0">
-        <v>3.77</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="338">
@@ -3841,7 +3847,7 @@
         <v>338</v>
       </c>
       <c r="B338" t="n" s="0">
-        <v>6.09</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="339">
@@ -3849,7 +3855,7 @@
         <v>339</v>
       </c>
       <c r="B339" t="n" s="0">
-        <v>1.21</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="340">
@@ -3857,7 +3863,7 @@
         <v>340</v>
       </c>
       <c r="B340" t="n" s="0">
-        <v>9.06</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="341">
@@ -3865,7 +3871,7 @@
         <v>341</v>
       </c>
       <c r="B341" t="n" s="0">
-        <v>7.69</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="342">
@@ -3873,7 +3879,7 @@
         <v>342</v>
       </c>
       <c r="B342" t="n" s="0">
-        <v>7.26</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="343">
@@ -3881,7 +3887,7 @@
         <v>343</v>
       </c>
       <c r="B343" t="n" s="0">
-        <v>8.1</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="344">
@@ -3889,7 +3895,7 @@
         <v>344</v>
       </c>
       <c r="B344" t="n" s="0">
-        <v>5.51</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="345">
@@ -3897,7 +3903,7 @@
         <v>345</v>
       </c>
       <c r="B345" t="n" s="0">
-        <v>15.51</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="346">
@@ -3905,7 +3911,7 @@
         <v>346</v>
       </c>
       <c r="B346" t="n" s="0">
-        <v>5.15</v>
+        <v>8.55</v>
       </c>
     </row>
     <row r="347">
@@ -3913,7 +3919,7 @@
         <v>347</v>
       </c>
       <c r="B347" t="n" s="0">
-        <v>6.04</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="348">
@@ -3921,7 +3927,7 @@
         <v>348</v>
       </c>
       <c r="B348" t="n" s="0">
-        <v>14.05</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="349">
@@ -3929,7 +3935,7 @@
         <v>349</v>
       </c>
       <c r="B349" t="n" s="0">
-        <v>6.67</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="350">
@@ -3937,7 +3943,7 @@
         <v>350</v>
       </c>
       <c r="B350" t="n" s="0">
-        <v>2.38</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="351">
@@ -3945,7 +3951,7 @@
         <v>351</v>
       </c>
       <c r="B351" t="n" s="0">
-        <v>9.43</v>
+        <v>14.05</v>
       </c>
     </row>
     <row r="352">
@@ -3953,7 +3959,7 @@
         <v>352</v>
       </c>
       <c r="B352" t="n" s="0">
-        <v>7.72</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="353">
@@ -3961,7 +3967,7 @@
         <v>353</v>
       </c>
       <c r="B353" t="n" s="0">
-        <v>9.4</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="354">
@@ -3969,7 +3975,7 @@
         <v>354</v>
       </c>
       <c r="B354" t="n" s="0">
-        <v>3.41</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="355">
@@ -3977,7 +3983,7 @@
         <v>355</v>
       </c>
       <c r="B355" t="n" s="0">
-        <v>3.5700000000000003</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="356">
@@ -3985,7 +3991,7 @@
         <v>356</v>
       </c>
       <c r="B356" t="n" s="0">
-        <v>9.98</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="357">
@@ -3993,7 +3999,7 @@
         <v>357</v>
       </c>
       <c r="B357" t="n" s="0">
-        <v>4.36</v>
+        <v>3.5700000000000003</v>
       </c>
     </row>
     <row r="358">
@@ -4001,6 +4007,22 @@
         <v>358</v>
       </c>
       <c r="B358" t="n" s="0">
+        <v>9.98</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="B359" t="n" s="0">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="s" s="0">
+        <v>360</v>
+      </c>
+      <c r="B360" t="n" s="0">
         <v>3.65</v>
       </c>
     </row>

--- a/tasks/AnalyticalCase/output/WeeklyEffortPerProject.xlsx
+++ b/tasks/AnalyticalCase/output/WeeklyEffortPerProject.xlsx
@@ -3415,7 +3415,7 @@
         <v>284</v>
       </c>
       <c r="B284" t="n" s="0">
-        <v>15.88</v>
+        <v>15.879999999999997</v>
       </c>
     </row>
     <row r="285">
